--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37B.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>49000</t>
   </si>
@@ -70,6 +70,12 @@
     <t>436786</t>
   </si>
   <si>
+    <t>571940</t>
+  </si>
+  <si>
+    <t>571941</t>
+  </si>
+  <si>
     <t>436787</t>
   </si>
   <si>
@@ -106,6 +112,12 @@
     <t>Número total de participantes</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de participantes mujeres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de participantes hombres</t>
+  </si>
+  <si>
     <t>Respuesta del sujeto obligado a los resultados, descripción sintética de lo que se tomó en cuenta</t>
   </si>
   <si>
@@ -121,31 +133,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>Ver nota</t>
-  </si>
-  <si>
-    <t>Ver note</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>5CB649614FE3E4571D54C155CBADBA16</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>11/10/2022</t>
-  </si>
-  <si>
-    <t>Del periodo 01/07/2022 al 30/09/2022 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
+    <t>5A96FB3450F1D338D5850A8DCAC4748D</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>Subdirección de Actividades Paraescolares</t>
+  </si>
+  <si>
+    <t>24/10/2023</t>
+  </si>
+  <si>
+    <t>Del periodo 01 de julio del 2023 al 30 de septiembre del 2023, El Colegio de Bachilleres del Estado de Tlaxcala a través de la Subdirección de Actividades Paraescolares no se generarón mecanismos de participación ciudadana, con referencia a los artículos 29 y 30 del Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala, toda vez que dentro de sus facultades del organismo desconcentrado, no efectúa este tipo de actividades, en consecuencia no cuenta con un hipervinculo.</t>
   </si>
 </sst>
 </file>
@@ -538,29 +547,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="82.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="255" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="82.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -577,7 +587,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -592,7 +602,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -612,22 +622,28 @@
         <v>9</v>
       </c>
       <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>8</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>7</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -661,10 +677,16 @@
       <c r="L5" t="s">
         <v>22</v>
       </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -677,83 +699,97 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A6:N6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
